--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
   <si>
     <t/>
   </si>
@@ -79,36 +79,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>20122091</t>
-  </si>
-  <si>
-    <t>KAHF FC.SCRB G/E 100</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10020713</t>
-  </si>
-  <si>
-    <t>WG COCO CUBE CP 1KG</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10021003</t>
-  </si>
-  <si>
-    <t>W/COCO CCPD SLC 1KG</t>
-  </si>
-  <si>
     <t>10006260</t>
   </si>
   <si>
@@ -127,28 +97,52 @@
     <t>MY/B WIPES ANTBC 2'S</t>
   </si>
   <si>
-    <t>10010805</t>
-  </si>
-  <si>
-    <t>SANIA MNYK GR PCH 2L</t>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
-  </si>
-  <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20136586</t>
+  </si>
+  <si>
+    <t>H&amp;S 2IN1 MNTHL 160</t>
+  </si>
+  <si>
+    <t>20138023</t>
+  </si>
+  <si>
+    <t>H&amp;S 2IN1 SUTERA 160</t>
+  </si>
+  <si>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -541,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -705,10 +699,10 @@
         <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -725,18 +719,18 @@
         <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -745,150 +739,130 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="47">
   <si>
     <t/>
   </si>
   <si>
-    <t>20045422</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L28</t>
+    <t>20077483</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS26 XL</t>
   </si>
   <si>
     <t>EG3A</t>
@@ -28,25 +28,25 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20045419</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M32</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20136706</t>
-  </si>
-  <si>
-    <t>IDM BABY DPRS L28</t>
+    <t>20073639</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE L/28'S</t>
   </si>
   <si>
     <t>3</t>
@@ -55,94 +55,103 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO ENR 780G</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20035629</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+VNL BOX350</t>
-  </si>
-  <si>
-    <t>10009496</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 350</t>
+    <t>20082394</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ MDU700</t>
+  </si>
+  <si>
+    <t>10009493</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 390G</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
+  </si>
+  <si>
+    <t>10025373</t>
+  </si>
+  <si>
+    <t>ENTRASOL GOLD VAN170</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20113913</t>
+  </si>
+  <si>
+    <t>MY/B WIPES ANTBC 2'S</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 780</t>
-  </si>
-  <si>
-    <t>20136510</t>
-  </si>
-  <si>
-    <t>MILO 3IN1 ACT-GO 400</t>
-  </si>
-  <si>
-    <t>20113913</t>
-  </si>
-  <si>
-    <t>MY/B WIPES ANTBC 2'S</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
+    <t>20137314</t>
+  </si>
+  <si>
+    <t>C/LANG TELON NAT.150</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20136586</t>
-  </si>
-  <si>
-    <t>H&amp;S 2IN1 MNTHL 160</t>
-  </si>
-  <si>
-    <t>20138023</t>
-  </si>
-  <si>
-    <t>H&amp;S 2IN1 SUTERA 160</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
-  </si>
-  <si>
     <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20013772</t>
+  </si>
+  <si>
+    <t>JOHNSON COLG SUMR100</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10006262</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10015652</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
+  </si>
+  <si>
+    <t>20010381</t>
+  </si>
+  <si>
+    <t>LIFEBUOY SHP A/D 170</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20028001</t>
+  </si>
+  <si>
+    <t>LFEBUOY SHP S&amp;SH 170</t>
   </si>
 </sst>
 </file>
@@ -535,14 +544,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -676,10 +685,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
@@ -687,10 +696,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -702,15 +711,15 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -722,7 +731,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -739,130 +748,150 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="50">
   <si>
     <t/>
   </si>
@@ -131,6 +131,15 @@
   </si>
   <si>
     <t>DNCOW 1+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>RT</t>
   </si>
   <si>
     <t>20135746</t>
@@ -544,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -845,21 +854,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -868,10 +877,10 @@
         <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -888,10 +897,30 @@
         <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
   <si>
     <t/>
   </si>
@@ -121,46 +121,49 @@
     <t>6</t>
   </si>
   <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10015652</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
-  </si>
-  <si>
-    <t>20010381</t>
-  </si>
-  <si>
-    <t>LIFEBUOY SHP A/D 170</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20028001</t>
-  </si>
-  <si>
-    <t>LFEBUOY SHP S&amp;SH 170</t>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
+  </si>
+  <si>
+    <t>20024079</t>
+  </si>
+  <si>
+    <t>TELUR AYM NEGERI BKL</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
   </si>
 </sst>
 </file>
@@ -560,7 +563,7 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -840,35 +843,35 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -877,18 +880,18 @@
         <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -897,10 +900,10 @@
         <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -917,10 +920,10 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
   <si>
     <t/>
   </si>
   <si>
-    <t>20077483</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS26 XL</t>
+    <t>20121399</t>
+  </si>
+  <si>
+    <t>MAMY POKO SC L 28'S</t>
   </si>
   <si>
     <t>EG3A</t>
@@ -28,142 +28,142 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20136706</t>
+  </si>
+  <si>
+    <t>IDM BABY DPRS L28</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20097385</t>
+  </si>
+  <si>
+    <t>HAPPY NAPPY PANT 32M</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20045419</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD M32</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 780</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10009496</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 350</t>
+  </si>
+  <si>
+    <t>20071686</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ MADU 700G</t>
+  </si>
+  <si>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 600</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
+    <t>20132006</t>
+  </si>
+  <si>
+    <t>P/AVT BTLE PLN 125ML</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20049629</t>
+  </si>
+  <si>
+    <t>C/LANG TELONLANG 60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-7B)</t>
+  </si>
+  <si>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
+  </si>
+  <si>
+    <t>20011007</t>
+  </si>
+  <si>
+    <t>LFBUOY BW M.CARE 400</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20073639</t>
-  </si>
-  <si>
-    <t>SWEETY BRONZE L/28'S</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO ENR 780G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20082394</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ MDU700</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 390G</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
-  </si>
-  <si>
-    <t>10025373</t>
-  </si>
-  <si>
-    <t>ENTRASOL GOLD VAN170</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20113913</t>
-  </si>
-  <si>
-    <t>MY/B WIPES ANTBC 2'S</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20137314</t>
-  </si>
-  <si>
-    <t>C/LANG TELON NAT.150</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20013772</t>
-  </si>
-  <si>
-    <t>JOHNSON COLG SUMR100</t>
+    <t>20011008</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 400</t>
+  </si>
+  <si>
+    <t>20040217</t>
+  </si>
+  <si>
+    <t>LFBUOY BW C.FRSH 400</t>
+  </si>
+  <si>
+    <t>20041399</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 400</t>
+  </si>
+  <si>
+    <t>20037413</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLS 90</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
-  </si>
-  <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
-  </si>
-  <si>
-    <t>20024079</t>
-  </si>
-  <si>
-    <t>TELUR AYM NEGERI BKL</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
+    <t>20070711</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS32 M</t>
+  </si>
+  <si>
+    <t>20070712</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS28 L</t>
   </si>
 </sst>
 </file>
@@ -556,14 +556,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>16</v>
@@ -697,10 +697,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
@@ -717,21 +717,21 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -740,10 +740,10 @@
         <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,10 +760,10 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -808,22 +808,22 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -837,81 +837,81 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -920,10 +920,30 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
   <si>
     <t/>
   </si>
@@ -112,10 +112,40 @@
     <t>RT,(E-7B)</t>
   </si>
   <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20040217</t>
+  </si>
+  <si>
+    <t>LFBUOY BW C.FRSH 400</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20011008</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 400</t>
+  </si>
+  <si>
+    <t>20041399</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 400</t>
   </si>
   <si>
     <t>20011007</t>
@@ -124,46 +154,28 @@
     <t>LFBUOY BW M.CARE 400</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20011008</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 400</t>
-  </si>
-  <si>
-    <t>20040217</t>
-  </si>
-  <si>
-    <t>LFBUOY BW C.FRSH 400</t>
-  </si>
-  <si>
-    <t>20041399</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 400</t>
-  </si>
-  <si>
-    <t>20037413</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLS 90</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
-    <t>20070711</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS32 M</t>
-  </si>
-  <si>
-    <t>20070712</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS28 L</t>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20117981</t>
+  </si>
+  <si>
+    <t>VIDORAN XM3+ VNL900</t>
   </si>
 </sst>
 </file>
@@ -556,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -803,15 +815,15 @@
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -823,7 +835,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -843,15 +855,15 @@
         <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -863,15 +875,15 @@
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -883,15 +895,15 @@
         <v>31</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -900,18 +912,18 @@
         <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -923,15 +935,15 @@
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -943,7 +955,27 @@
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t/>
   </si>
   <si>
-    <t>20121399</t>
-  </si>
-  <si>
-    <t>MAMY POKO SC L 28'S</t>
+    <t>20097386</t>
+  </si>
+  <si>
+    <t>HAPPY NAPPY PANT 28L</t>
   </si>
   <si>
     <t>EG3A</t>
@@ -28,154 +28,127 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20045419</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M32</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO ENR 780G</t>
+  </si>
+  <si>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 780</t>
+  </si>
+  <si>
+    <t>10009493</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 390G</t>
+  </si>
+  <si>
+    <t>20113913</t>
+  </si>
+  <si>
+    <t>MY/B WIPES ANTBC 2'S</t>
+  </si>
+  <si>
+    <t>20138272</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE SB 2X50</t>
+  </si>
+  <si>
+    <t>20137940</t>
+  </si>
+  <si>
+    <t>VICKS BABY BALM 20G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20141440</t>
+  </si>
+  <si>
+    <t>C.LANG MK BAYI CHM60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20141441</t>
+  </si>
+  <si>
+    <t>C.LANG MK.BAYI LVD60</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10006262</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10015652</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>20048847</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP900</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20136706</t>
-  </si>
-  <si>
-    <t>IDM BABY DPRS L28</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20097385</t>
-  </si>
-  <si>
-    <t>HAPPY NAPPY PANT 32M</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 780</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10009496</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>20071686</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ MADU 700G</t>
-  </si>
-  <si>
-    <t>20074147</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 600</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
-  </si>
-  <si>
-    <t>20132006</t>
-  </si>
-  <si>
-    <t>P/AVT BTLE PLN 125ML</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20049629</t>
-  </si>
-  <si>
-    <t>C/LANG TELONLANG 60</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-7B)</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20040217</t>
-  </si>
-  <si>
-    <t>LFBUOY BW C.FRSH 400</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20011008</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 400</t>
-  </si>
-  <si>
-    <t>20041399</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 400</t>
-  </si>
-  <si>
-    <t>20011007</t>
-  </si>
-  <si>
-    <t>LFBUOY BW M.CARE 400</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 900</t>
-  </si>
-  <si>
-    <t>20117981</t>
-  </si>
-  <si>
-    <t>VIDORAN XM3+ VNL900</t>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
+    <t>20024079</t>
+  </si>
+  <si>
+    <t>TELUR AYM NEGERI BKL</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
   </si>
 </sst>
 </file>
@@ -568,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -675,15 +648,15 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -695,55 +668,55 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -752,18 +725,18 @@
         <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -772,18 +745,18 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -792,87 +765,87 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>40</v>
@@ -880,19 +853,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
@@ -900,82 +873,22 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
   <si>
     <t/>
   </si>
@@ -115,40 +115,34 @@
     <t>6</t>
   </si>
   <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10015652</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
-  </si>
-  <si>
-    <t>20024079</t>
-  </si>
-  <si>
-    <t>TELUR AYM NEGERI BKL</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
+    <t>20002944</t>
+  </si>
+  <si>
+    <t>PPSODENT HERBAL 190G</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20040296</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 900</t>
+  </si>
+  <si>
+    <t>20040295</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 900G</t>
   </si>
 </sst>
 </file>
@@ -541,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -808,15 +802,15 @@
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -828,35 +822,35 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -865,30 +859,10 @@
         <v>30</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,138 +11,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
   <si>
     <t/>
   </si>
   <si>
+    <t>20106150</t>
+  </si>
+  <si>
+    <t>MAMY POKO 44'S NB</t>
+  </si>
+  <si>
+    <t>EG3A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20137023</t>
+  </si>
+  <si>
+    <t>SWEETY X-PERT L-38</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>20097386</t>
   </si>
   <si>
     <t>HAPPY NAPPY PANT 28L</t>
   </si>
   <si>
-    <t>EG3A</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20045419</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD M32</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20082594</t>
+  </si>
+  <si>
+    <t>BEBELAC GLD3 VAN700</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10015653</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>20037098</t>
+  </si>
+  <si>
+    <t>SGM SOYA 1+ VANL 400</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20138273</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE AF 2X50</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO ENR 780G</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 780</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 390G</t>
-  </si>
-  <si>
-    <t>20113913</t>
-  </si>
-  <si>
-    <t>MY/B WIPES ANTBC 2'S</t>
-  </si>
-  <si>
-    <t>20138272</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE SB 2X50</t>
-  </si>
-  <si>
-    <t>20137940</t>
-  </si>
-  <si>
-    <t>VICKS BABY BALM 20G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20141440</t>
-  </si>
-  <si>
-    <t>C.LANG MK BAYI CHM60</t>
+    <t>20018225</t>
+  </si>
+  <si>
+    <t>JHNSON BDTM BATH 400</t>
+  </si>
+  <si>
+    <t>20003395</t>
+  </si>
+  <si>
+    <t>JHNSN H&amp;B MLK+RC 400</t>
+  </si>
+  <si>
+    <t>20037413</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLS 90</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20141441</t>
-  </si>
-  <si>
-    <t>C.LANG MK.BAYI LVD60</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20002944</t>
-  </si>
-  <si>
-    <t>PPSODENT HERBAL 190G</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20040296</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 900</t>
-  </si>
-  <si>
-    <t>20040295</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 900G</t>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20136707</t>
+  </si>
+  <si>
+    <t>IDM DPRS PANTS M32</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20125783</t>
+  </si>
+  <si>
+    <t>CAP/ENAK KKM PTH 535</t>
+  </si>
+  <si>
+    <t>20136706</t>
+  </si>
+  <si>
+    <t>IDM BABY DPRS L28</t>
   </si>
 </sst>
 </file>
@@ -622,15 +619,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -639,10 +636,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -659,10 +656,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -676,21 +673,21 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -702,15 +699,15 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -727,10 +724,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -739,10 +736,10 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -762,7 +759,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -776,13 +773,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -796,41 +793,41 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -842,15 +839,15 @@
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -862,7 +859,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
   <si>
     <t/>
   </si>
   <si>
-    <t>20106150</t>
-  </si>
-  <si>
-    <t>MAMY POKO 44'S NB</t>
+    <t>20045422</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L28</t>
   </si>
   <si>
     <t>EG3A</t>
@@ -28,118 +28,142 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20137023</t>
+  </si>
+  <si>
+    <t>SWEETY X-PERT L-38</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20097385</t>
+  </si>
+  <si>
+    <t>HAPPY NAPPY PANT 32M</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20040294</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 900</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>10013035</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10009493</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 390G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20113913</t>
+  </si>
+  <si>
+    <t>MY/B WIPES ANTBC 2'S</t>
+  </si>
+  <si>
+    <t>20035884</t>
+  </si>
+  <si>
+    <t>CUSSONS HL.NAT KM100</t>
+  </si>
+  <si>
+    <t>20040710</t>
+  </si>
+  <si>
+    <t>KONICARE TELON PLS60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20122064</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLS LV60</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20097386</t>
-  </si>
-  <si>
-    <t>HAPPY NAPPY PANT 28L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20082594</t>
-  </si>
-  <si>
-    <t>BEBELAC GLD3 VAN700</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10015653</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>20037098</t>
-  </si>
-  <si>
-    <t>SGM SOYA 1+ VANL 400</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20138273</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE AF 2X50</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20018225</t>
-  </si>
-  <si>
-    <t>JHNSON BDTM BATH 400</t>
-  </si>
-  <si>
-    <t>20003395</t>
-  </si>
-  <si>
-    <t>JHNSN H&amp;B MLK+RC 400</t>
-  </si>
-  <si>
-    <t>20037413</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLS 90</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
+    <t>20137761</t>
+  </si>
+  <si>
+    <t>LARISST CRISPY CHO50</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20136707</t>
-  </si>
-  <si>
-    <t>IDM DPRS PANTS M32</t>
+    <t>20133192</t>
+  </si>
+  <si>
+    <t>ROCHO WFR CKLT KCG84</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20125783</t>
-  </si>
-  <si>
-    <t>CAP/ENAK KKM PTH 535</t>
-  </si>
-  <si>
-    <t>20136706</t>
-  </si>
-  <si>
-    <t>IDM BABY DPRS L28</t>
+    <t>20137064</t>
+  </si>
+  <si>
+    <t>IDM CND GUMMY PUZL50</t>
+  </si>
+  <si>
+    <t>20137681</t>
+  </si>
+  <si>
+    <t>IDM GUMMY STRW MGO50</t>
+  </si>
+  <si>
+    <t>20134695</t>
+  </si>
+  <si>
+    <t>PRMNA CRCKR BRRIES20</t>
   </si>
 </sst>
 </file>
@@ -532,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -636,7 +660,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>15</v>
@@ -656,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>15</v>
@@ -676,7 +700,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>15</v>
@@ -684,30 +708,30 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -724,10 +748,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -736,18 +760,18 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -756,10 +780,10 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -773,13 +797,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -793,13 +817,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -813,10 +837,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -833,33 +857,93 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,38 +11,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t/>
   </si>
   <si>
+    <t>20137023</t>
+  </si>
+  <si>
+    <t>SWEETY X-PERT L-38</t>
+  </si>
+  <si>
+    <t>EG3A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>20045422</t>
   </si>
   <si>
     <t>MAMY/P PANTS STD L28</t>
   </si>
   <si>
-    <t>EG3A</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>2</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
     <t>20097385</t>
   </si>
   <si>
@@ -52,118 +52,172 @@
     <t>3</t>
   </si>
   <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 780</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
-  </si>
-  <si>
-    <t>10013035</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 390G</t>
+    <t>10006258</t>
+  </si>
+  <si>
+    <t>DNCOWFRTGO F.CR 780G</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20113913</t>
-  </si>
-  <si>
-    <t>MY/B WIPES ANTBC 2'S</t>
-  </si>
-  <si>
-    <t>20035884</t>
-  </si>
-  <si>
-    <t>CUSSONS HL.NAT KM100</t>
-  </si>
-  <si>
-    <t>20040710</t>
-  </si>
-  <si>
-    <t>KONICARE TELON PLS60</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20003395</t>
+  </si>
+  <si>
+    <t>JHNSN H&amp;B MLK+RC 400</t>
+  </si>
+  <si>
+    <t>20138273</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE AF 2X50</t>
+  </si>
+  <si>
+    <t>20140018</t>
+  </si>
+  <si>
+    <t>IDM BB.WIPE RM 2X50S</t>
+  </si>
+  <si>
+    <t>20113917</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC SWT 100</t>
+  </si>
+  <si>
+    <t>20113918</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC FRSH100</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20122064</t>
-  </si>
-  <si>
-    <t>MY BABY TLN PLS LV60</t>
+    <t>20135607</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC LVELY100</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
-  </si>
-  <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20137761</t>
-  </si>
-  <si>
-    <t>LARISST CRISPY CHO50</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20133192</t>
-  </si>
-  <si>
-    <t>ROCHO WFR CKLT KCG84</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20137064</t>
-  </si>
-  <si>
-    <t>IDM CND GUMMY PUZL50</t>
-  </si>
-  <si>
-    <t>20137681</t>
-  </si>
-  <si>
-    <t>IDM GUMMY STRW MGO50</t>
-  </si>
-  <si>
-    <t>20134695</t>
-  </si>
-  <si>
-    <t>PRMNA CRCKR BRRIES20</t>
+    <t>20125041</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLS LV90</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20137314</t>
+  </si>
+  <si>
+    <t>C/LANG TELON NAT.150</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
+  </si>
+  <si>
+    <t>20137572</t>
+  </si>
+  <si>
+    <t>CHTATO LITE KEJU 110</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20137054</t>
+  </si>
+  <si>
+    <t>CHTATO LITE ASLI 110</t>
+  </si>
+  <si>
+    <t>20025825</t>
+  </si>
+  <si>
+    <t>PRONAS KORNETKU 200G</t>
+  </si>
+  <si>
+    <t>20054917</t>
+  </si>
+  <si>
+    <t>ELLIP H.VIT K/REP6'S</t>
+  </si>
+  <si>
+    <t>20005532</t>
+  </si>
+  <si>
+    <t>ELIP H.VT HAIR/TR 6S</t>
+  </si>
+  <si>
+    <t>20055603</t>
+  </si>
+  <si>
+    <t>ELLIPS PRO-K S&amp;S 6'S</t>
+  </si>
+  <si>
+    <t>20055602</t>
+  </si>
+  <si>
+    <t>ELLIPS H.VIT K/SIL6S</t>
   </si>
 </sst>
 </file>
@@ -556,14 +610,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -643,7 +697,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -723,15 +777,15 @@
         <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -740,18 +794,18 @@
         <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -760,18 +814,18 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -780,19 +834,19 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
@@ -800,67 +854,67 @@
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>41</v>
@@ -877,73 +931,213 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,213 +11,198 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
   <si>
     <t/>
   </si>
   <si>
+    <t>20045422</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD L28</t>
+  </si>
+  <si>
+    <t>EG3A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20095874</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 30'S M</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20137023</t>
   </si>
   <si>
     <t>SWEETY X-PERT L-38</t>
   </si>
   <si>
-    <t>EG3A</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20045422</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L28</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20097385</t>
-  </si>
-  <si>
-    <t>HAPPY NAPPY PANT 32M</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 780</t>
+    <t>20040294</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 900</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10006258</t>
-  </si>
-  <si>
-    <t>DNCOWFRTGO F.CR 780G</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 900</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>20033353</t>
+  </si>
+  <si>
+    <t>HILO/S HI-CAL CHO250</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>20069146</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MDU BX1000</t>
+  </si>
+  <si>
+    <t>20136510</t>
+  </si>
+  <si>
+    <t>MILO 3IN1 ACT-GO 400</t>
+  </si>
+  <si>
+    <t>20138273</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE AF 2X50</t>
+  </si>
+  <si>
+    <t>20135637</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B WSH 300</t>
+  </si>
+  <si>
+    <t>20027095</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLS 60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20115153</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE A/B50S</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20003395</t>
-  </si>
-  <si>
-    <t>JHNSN H&amp;B MLK+RC 400</t>
-  </si>
-  <si>
-    <t>20138273</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE AF 2X50</t>
-  </si>
-  <si>
-    <t>20140018</t>
-  </si>
-  <si>
-    <t>IDM BB.WIPE RM 2X50S</t>
-  </si>
-  <si>
-    <t>20113917</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC SWT 100</t>
-  </si>
-  <si>
-    <t>20113918</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC FRSH100</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20135607</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC LVELY100</t>
+    <t>20134049</t>
+  </si>
+  <si>
+    <t>KODOMO BB H&amp;B ALO400</t>
+  </si>
+  <si>
+    <t>20133137</t>
+  </si>
+  <si>
+    <t>MY BB FC&amp;BDY NOURI50</t>
+  </si>
+  <si>
+    <t>20132819</t>
+  </si>
+  <si>
+    <t>BLGIO PMDE BBLGUM 40</t>
+  </si>
+  <si>
+    <t>20017976</t>
+  </si>
+  <si>
+    <t>JHNSON BDTM BATH 200</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20125041</t>
-  </si>
-  <si>
-    <t>MY BABY TLN PLS LV90</t>
+    <t>20071630</t>
+  </si>
+  <si>
+    <t>JOHNSON SHP SHNY 100</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142282</t>
+  </si>
+  <si>
+    <t>CLOSEUP PG FIFA 95G</t>
+  </si>
+  <si>
+    <t>20113913</t>
+  </si>
+  <si>
+    <t>MY/B WIPES ANTBC 2'S</t>
+  </si>
+  <si>
+    <t>20077369</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BLUBR 15</t>
+  </si>
+  <si>
+    <t>20047037</t>
+  </si>
+  <si>
+    <t>IDM KACANG BALI 150G</t>
+  </si>
+  <si>
+    <t>10005701</t>
+  </si>
+  <si>
+    <t>BOTAN PREMIUM 155GR</t>
+  </si>
+  <si>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
+  </si>
+  <si>
     <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20137314</t>
-  </si>
-  <si>
-    <t>C/LANG TELON NAT.150</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>20137572</t>
-  </si>
-  <si>
-    <t>CHTATO LITE KEJU 110</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20137054</t>
-  </si>
-  <si>
-    <t>CHTATO LITE ASLI 110</t>
-  </si>
-  <si>
-    <t>20025825</t>
-  </si>
-  <si>
-    <t>PRONAS KORNETKU 200G</t>
-  </si>
-  <si>
-    <t>20054917</t>
-  </si>
-  <si>
-    <t>ELLIP H.VIT K/REP6'S</t>
-  </si>
-  <si>
-    <t>20005532</t>
-  </si>
-  <si>
-    <t>ELIP H.VT HAIR/TR 6S</t>
-  </si>
-  <si>
-    <t>20055603</t>
-  </si>
-  <si>
-    <t>ELLIPS PRO-K S&amp;S 6'S</t>
-  </si>
-  <si>
-    <t>20055602</t>
-  </si>
-  <si>
-    <t>ELLIPS H.VIT K/SIL6S</t>
   </si>
 </sst>
 </file>
@@ -610,14 +595,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -697,15 +682,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -717,15 +702,15 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -737,15 +722,15 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -754,30 +739,30 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -794,10 +779,10 @@
         <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -814,10 +799,10 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -834,10 +819,10 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -854,50 +839,50 @@
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -911,233 +896,213 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="66">
   <si>
     <t/>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138144</t>
+  </si>
+  <si>
+    <t>KODOMO WPS H&amp;M 2X50S</t>
   </si>
   <si>
     <t>20134049</t>
@@ -595,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -879,10 +885,10 @@
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -899,10 +905,10 @@
         <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -919,7 +925,7 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>13</v>
@@ -939,7 +945,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>13</v>
@@ -947,10 +953,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -959,7 +965,7 @@
         <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
@@ -967,30 +973,30 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -999,10 +1005,10 @@
         <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1019,10 +1025,10 @@
         <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1039,10 +1045,10 @@
         <v>32</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1059,10 +1065,10 @@
         <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1079,10 +1085,10 @@
         <v>32</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1099,10 +1105,30 @@
         <v>32</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
   <si>
     <t/>
   </si>
@@ -31,10 +31,10 @@
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20095874</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 30'S M</t>
+    <t>20095875</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 28'S L</t>
   </si>
   <si>
     <t>2</t>
@@ -43,10 +43,10 @@
     <t>PT</t>
   </si>
   <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
+    <t>20137024</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT M-44</t>
   </si>
   <si>
     <t>3</t>
@@ -55,160 +55,130 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
+    <t>20098370</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU325</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
-  </si>
-  <si>
-    <t>20033353</t>
-  </si>
-  <si>
-    <t>HILO/S HI-CAL CHO250</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20069146</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MDU BX1000</t>
-  </si>
-  <si>
-    <t>20136510</t>
-  </si>
-  <si>
-    <t>MILO 3IN1 ACT-GO 400</t>
-  </si>
-  <si>
-    <t>20138273</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE AF 2X50</t>
-  </si>
-  <si>
-    <t>20135637</t>
-  </si>
-  <si>
-    <t>MY BABY H&amp;B WSH 300</t>
-  </si>
-  <si>
-    <t>20027095</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLS 60</t>
+    <t>20021571</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VAN 560G</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20092863</t>
+  </si>
+  <si>
+    <t>YB BABY CRCK STRW 25</t>
+  </si>
+  <si>
+    <t>20138272</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE SB 2X50</t>
+  </si>
+  <si>
+    <t>20082403</t>
+  </si>
+  <si>
+    <t>CL TELON LANG PLS150</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20046056</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLUS 150</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20115153</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE A/B50S</t>
+    <t>20091617</t>
+  </si>
+  <si>
+    <t>HUKI BTL PP SP RN240</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20138599</t>
+  </si>
+  <si>
+    <t>JETZ TOR JG.BKR 140G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20001605</t>
+  </si>
+  <si>
+    <t>ENRGEN CKLT PCK 10'S</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138144</t>
-  </si>
-  <si>
-    <t>KODOMO WPS H&amp;M 2X50S</t>
-  </si>
-  <si>
-    <t>20134049</t>
-  </si>
-  <si>
-    <t>KODOMO BB H&amp;B ALO400</t>
-  </si>
-  <si>
-    <t>20133137</t>
-  </si>
-  <si>
-    <t>MY BB FC&amp;BDY NOURI50</t>
-  </si>
-  <si>
-    <t>20132819</t>
-  </si>
-  <si>
-    <t>BLGIO PMDE BBLGUM 40</t>
-  </si>
-  <si>
-    <t>20017976</t>
-  </si>
-  <si>
-    <t>JHNSON BDTM BATH 200</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20071630</t>
-  </si>
-  <si>
-    <t>JOHNSON SHP SHNY 100</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
+    <t>20001604</t>
+  </si>
+  <si>
+    <t>ENRGEN VAN PCK 10'S</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
+  </si>
+  <si>
+    <t>20140912</t>
+  </si>
+  <si>
+    <t>SM TOLAK ANGIN 15ML</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
+  </si>
+  <si>
+    <t>20136643</t>
+  </si>
+  <si>
+    <t>PSODENT PG STRG 190G</t>
+  </si>
+  <si>
+    <t>20142282</t>
+  </si>
+  <si>
+    <t>CLOSEUP PG FIFA 95G</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20142282</t>
-  </si>
-  <si>
-    <t>CLOSEUP PG FIFA 95G</t>
-  </si>
-  <si>
-    <t>20113913</t>
-  </si>
-  <si>
-    <t>MY/B WIPES ANTBC 2'S</t>
-  </si>
-  <si>
-    <t>20077369</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BLUBR 15</t>
-  </si>
-  <si>
-    <t>20047037</t>
-  </si>
-  <si>
-    <t>IDM KACANG BALI 150G</t>
-  </si>
-  <si>
-    <t>10005701</t>
-  </si>
-  <si>
-    <t>BOTAN PREMIUM 155GR</t>
-  </si>
-  <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
   </si>
 </sst>
 </file>
@@ -601,14 +571,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -705,58 +675,58 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -765,18 +735,18 @@
         <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -785,18 +755,18 @@
         <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -805,18 +775,18 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -825,310 +795,190 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
   <si>
     <t/>
   </si>
   <si>
-    <t>20045422</t>
-  </si>
-  <si>
-    <t>MAMY/P PANTS STD L28</t>
+    <t>20095874</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 30'S M</t>
   </si>
   <si>
     <t>EG3A</t>
@@ -28,157 +28,118 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20073639</t>
+  </si>
+  <si>
+    <t>SWEETY BRONZE L/28'S</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20069147</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ VNL BX1000</t>
+  </si>
+  <si>
+    <t>20098371</t>
+  </si>
+  <si>
+    <t>VDORAN SUSU MADU 325</t>
+  </si>
+  <si>
+    <t>20098369</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN350</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138273</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE AF 2X50</t>
+  </si>
+  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20095875</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 28'S L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20137024</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT M-44</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20098370</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU325</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 560G</t>
+    <t>20091175</t>
+  </si>
+  <si>
+    <t>PEPSODNT KIDS STR 45</t>
+  </si>
+  <si>
+    <t>20052548</t>
+  </si>
+  <si>
+    <t>KONICARE TLN PLS 125</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20090437</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN700</t>
+  </si>
+  <si>
+    <t>20024079</t>
+  </si>
+  <si>
+    <t>TELUR AYM NEGERI BKL</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>10001365</t>
+  </si>
+  <si>
+    <t>NYAM2 STICK CHOCO 25</t>
+  </si>
+  <si>
+    <t>20029222</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BEEF50</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20092863</t>
-  </si>
-  <si>
-    <t>YB BABY CRCK STRW 25</t>
-  </si>
-  <si>
-    <t>20138272</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE SB 2X50</t>
-  </si>
-  <si>
-    <t>20082403</t>
-  </si>
-  <si>
-    <t>CL TELON LANG PLS150</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20046056</t>
-  </si>
-  <si>
-    <t>MY BABY TLN PLUS 150</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20091617</t>
-  </si>
-  <si>
-    <t>HUKI BTL PP SP RN240</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20138599</t>
-  </si>
-  <si>
-    <t>JETZ TOR JG.BKR 140G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20001605</t>
-  </si>
-  <si>
-    <t>ENRGEN CKLT PCK 10'S</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20001604</t>
-  </si>
-  <si>
-    <t>ENRGEN VAN PCK 10'S</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
-  </si>
-  <si>
-    <t>20140912</t>
-  </si>
-  <si>
-    <t>SM TOLAK ANGIN 15ML</t>
-  </si>
-  <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
-  </si>
-  <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
-  </si>
-  <si>
-    <t>20136643</t>
-  </si>
-  <si>
-    <t>PSODENT PG STRG 190G</t>
-  </si>
-  <si>
-    <t>20142282</t>
-  </si>
-  <si>
-    <t>CLOSEUP PG FIFA 95G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -571,17 +532,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,8 +562,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -617,11 +585,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -637,11 +605,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -657,11 +625,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -675,18 +643,18 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -695,18 +663,18 @@
         <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -715,33 +683,33 @@
         <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -752,36 +720,36 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -792,193 +760,93 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="H13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="43">
   <si>
     <t/>
   </si>
@@ -532,18 +532,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,14 +561,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -585,11 +578,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -605,11 +598,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -625,11 +618,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -645,11 +638,11 @@
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -665,11 +658,11 @@
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -685,11 +678,11 @@
       <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -705,11 +698,11 @@
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -725,11 +718,11 @@
       <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -745,11 +738,11 @@
       <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -765,11 +758,11 @@
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -785,11 +778,11 @@
       <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -805,11 +798,11 @@
       <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -825,11 +818,11 @@
       <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -845,7 +838,7 @@
       <c r="E15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/EG3A.xlsx
+++ b/EG3A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
   <si>
     <t/>
   </si>
   <si>
-    <t>20095874</t>
-  </si>
-  <si>
-    <t>MP PANTS T/G 30'S M</t>
+    <t>20045419</t>
+  </si>
+  <si>
+    <t>MAMY/P PANTS STD M32</t>
   </si>
   <si>
     <t>EG3A</t>
@@ -28,118 +28,175 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20095875</t>
+  </si>
+  <si>
+    <t>MP PANTS T/G 28'S L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20073639</t>
-  </si>
-  <si>
-    <t>SWEETY BRONZE L/28'S</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20137024</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT M-44</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20069147</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ VNL BX1000</t>
-  </si>
-  <si>
-    <t>20098371</t>
-  </si>
-  <si>
-    <t>VDORAN SUSU MADU 325</t>
-  </si>
-  <si>
-    <t>20098369</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN350</t>
+    <t>10009496</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 350</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138273</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE AF 2X50</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20091175</t>
-  </si>
-  <si>
-    <t>PEPSODNT KIDS STR 45</t>
-  </si>
-  <si>
-    <t>20052548</t>
-  </si>
-  <si>
-    <t>KONICARE TLN PLS 125</t>
+    <t>20138272</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE SB 2X50</t>
+  </si>
+  <si>
+    <t>20096977</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B WSH 200</t>
+  </si>
+  <si>
+    <t>20125041</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLS LV90</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20137314</t>
+  </si>
+  <si>
+    <t>C/LANG TELON NAT.150</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10011772</t>
+  </si>
+  <si>
+    <t>CUSSONS B/CRM MILD50</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20090437</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN700</t>
-  </si>
-  <si>
-    <t>20024079</t>
-  </si>
-  <si>
-    <t>TELUR AYM NEGERI BKL</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>10001365</t>
-  </si>
-  <si>
-    <t>NYAM2 STICK CHOCO 25</t>
-  </si>
-  <si>
-    <t>20029222</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BEEF50</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
+    <t>10033930</t>
+  </si>
+  <si>
+    <t>CUSSON B/CRM SOFT50</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20091617</t>
+  </si>
+  <si>
+    <t>HUKI BTL PP SP RN240</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20117981</t>
+  </si>
+  <si>
+    <t>VIDORAN XM3+ VNL900</t>
+  </si>
+  <si>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 5'S</t>
+  </si>
+  <si>
+    <t>20023765</t>
+  </si>
+  <si>
+    <t>FORMULA S/G FLIP MBL</t>
+  </si>
+  <si>
+    <t>20128951</t>
+  </si>
+  <si>
+    <t>MORRIS PMD EXTR HL80</t>
+  </si>
+  <si>
+    <t>20019631</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK 1L</t>
+  </si>
+  <si>
+    <t>20137054</t>
+  </si>
+  <si>
+    <t>CHTATO LITE ASLI 110</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20137572</t>
+  </si>
+  <si>
+    <t>CHTATO LITE KEJU 110</t>
+  </si>
+  <si>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP AYM BWG 5'S</t>
   </si>
 </sst>
 </file>
@@ -532,14 +589,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -636,70 +693,70 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -713,13 +770,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -733,33 +790,33 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -773,13 +830,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -793,53 +850,213 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>42</v>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
